--- a/data/trans_dic/IP31KM09_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM09_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,2; 98,77</t>
+          <t>88,79; 98,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>89,15; 98,48</t>
+          <t>91,25; 98,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91,97; 98,06</t>
+          <t>91,47; 98,0</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,1%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,45; 96,08</t>
+          <t>83,04; 94,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,88; 94,09</t>
+          <t>81,32; 92,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,4; 94,23</t>
+          <t>84,3; 92,32</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,27; 97,9</t>
+          <t>88,41; 98,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,12; 98,13</t>
+          <t>87,24; 98,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,64; 97,59</t>
+          <t>89,96; 97,52</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,69; 95,89</t>
+          <t>52,6; 96,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,1; 96,41</t>
+          <t>84,08; 96,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,64; 94,37</t>
+          <t>69,22; 94,91</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,26; 98,63</t>
+          <t>86,35; 98,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>84,73; 98,47</t>
+          <t>86,7; 98,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,32; 97,31</t>
+          <t>89,29; 97,41</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76,61; 92,18</t>
+          <t>78,07; 93,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80,84; 94,66</t>
+          <t>76,48; 92,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81,27; 92,34</t>
+          <t>80,39; 91,86</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>84,52; 94,04</t>
+          <t>85,81; 94,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,7; 94,88</t>
+          <t>83,88; 94,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,77; 93,79</t>
+          <t>86,7; 93,39</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>96,01; 99,6</t>
+          <t>98,69; 100,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>98,32; 100,0</t>
+          <t>96,65; 99,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97,92; 99,82</t>
+          <t>98,29; 99,82</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>91,03; 94,62</t>
+          <t>88,43; 94,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>86,42; 94,63</t>
+          <t>90,78; 94,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89,92; 94,01</t>
+          <t>90,52; 94,02</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>87</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68865</t>
+          <t>57575</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71415</t>
+          <t>52787</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140280</t>
+          <t>110363</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>65831; 70525</t>
+          <t>53508; 59614</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>66509; 73474</t>
+          <t>50118; 54145</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>134278; 143177</t>
+          <t>105363; 112880</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>121</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>113720</t>
+          <t>103517</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>113634</t>
+          <t>87410</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>227353</t>
+          <t>190927</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>106112; 120725</t>
+          <t>95451; 108220</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>104776; 118954</t>
+          <t>80782; 92096</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>217785; 237517</t>
+          <t>180637; 197822</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>86</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52484</t>
+          <t>54562</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61233</t>
+          <t>50932</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113717</t>
+          <t>105493</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>48478; 54386</t>
+          <t>50656; 56628</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>55016; 63421</t>
+          <t>47206; 53047</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107734; 117288</t>
+          <t>100224; 108652</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>84</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>63622</t>
+          <t>58234</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>61215</t>
+          <t>64859</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124836</t>
+          <t>123094</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58319; 66816</t>
+          <t>36726; 67553</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36253; 72663</t>
+          <t>59248; 67650</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86504; 136883</t>
+          <t>97100; 133144</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>63</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32342</t>
+          <t>37278</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38369</t>
+          <t>33496</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70711</t>
+          <t>70775</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29499; 33732</t>
+          <t>34175; 38977</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34502; 40095</t>
+          <t>30667; 34891</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66917; 72904</t>
+          <t>66919; 73008</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>38043</t>
+          <t>41217</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>47667</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85709</t>
+          <t>79441</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33931; 40826</t>
+          <t>36857; 44092</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43479; 50912</t>
+          <t>33871; 41092</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>79706; 90558</t>
+          <t>73551; 84049</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>158</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>111484</t>
+          <t>127765</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>142130</t>
+          <t>109144</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>253613</t>
+          <t>236910</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>104552; 116327</t>
+          <t>120630; 132860</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>134416; 147104</t>
+          <t>102179; 114531</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>244659; 261429</t>
+          <t>227495; 245063</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>181</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>126819</t>
+          <t>156709</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>153648</t>
+          <t>136295</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>280466</t>
+          <t>293003</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>123529; 128155</t>
+          <t>155074; 157136</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>151571; 154159</t>
+          <t>133285; 137465</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>276928; 282308</t>
+          <t>289983; 294505</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>844</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>879</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>607377</t>
+          <t>636857</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>689310</t>
+          <t>573148</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1296687</t>
+          <t>1210004</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>594531; 618007</t>
+          <t>607353; 650829</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>643635; 704732</t>
+          <t>561227; 582761</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1256992; 1314187</t>
+          <t>1181271; 1226927</t>
         </is>
       </c>
     </row>
